--- a/electron/data/summary.xlsx
+++ b/electron/data/summary.xlsx
@@ -475,16 +475,16 @@
         <v>178.81973275531917</v>
       </c>
       <c r="I2">
-        <v>217.87</v>
+        <v>219.49</v>
       </c>
       <c r="J2">
-        <v>5.55</v>
+        <v>-2.19</v>
       </c>
       <c r="K2" t="str">
-        <v>(2.61%)</v>
+        <v>(-0.99%)</v>
       </c>
       <c r="L2">
-        <v>21.837784143271097</v>
+        <v>22.74372443019495</v>
       </c>
       <c r="M2">
         <v>10.42753148506382</v>
@@ -522,16 +522,16 @@
         <v>222.71513564555553</v>
       </c>
       <c r="I3">
-        <v>404.15</v>
+        <v>437</v>
       </c>
       <c r="J3">
-        <v>3.86</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="str">
-        <v>(0.96%)</v>
+        <v>(0.23%)</v>
       </c>
       <c r="L3">
-        <v>81.46499061617105</v>
+        <v>96.21477396824632</v>
       </c>
       <c r="M3">
         <v>36.84314366452076</v>
@@ -569,16 +569,16 @@
         <v>14.116166666666667</v>
       </c>
       <c r="I4">
-        <v>16.9</v>
+        <v>17.45</v>
       </c>
       <c r="J4">
-        <v>0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="K4" t="str">
-        <v>(0.84%)</v>
+        <v>(-0.63%)</v>
       </c>
       <c r="L4">
-        <v>19.72088739860915</v>
+        <v>23.617129296197028</v>
       </c>
       <c r="M4">
         <v>8.756992788986127</v>
@@ -601,7 +601,7 @@
         <v>Mari Energies Limited</v>
       </c>
       <c r="D5" t="str">
-        <v>XD</v>
+        <v/>
       </c>
       <c r="E5" t="str">
         <v>OIL &amp; GAS EXPLORATION COMPANIES</v>
@@ -616,16 +616,16 @@
         <v>601.8757826767677</v>
       </c>
       <c r="I5">
-        <v>706.4</v>
+        <v>760.9</v>
       </c>
       <c r="J5">
-        <v>18.78</v>
+        <v>19.86</v>
       </c>
       <c r="K5" t="str">
-        <v>(2.73%)</v>
+        <v>(2.68%)</v>
       </c>
       <c r="L5">
-        <v>17.36641020151597</v>
+        <v>26.42143477114029</v>
       </c>
       <c r="M5">
         <v>24.64274139522381</v>
@@ -663,16 +663,16 @@
         <v>25.82693091549296</v>
       </c>
       <c r="I6">
-        <v>32.03</v>
+        <v>32</v>
       </c>
       <c r="J6">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="K6" t="str">
-        <v>(-0.06%)</v>
+        <v>(-0.28%)</v>
       </c>
       <c r="L6">
-        <v>24.017832799428636</v>
+        <v>23.90167497913569</v>
       </c>
       <c r="M6">
         <v>7.583646926333468</v>
@@ -710,16 +710,16 @@
         <v>17.5295</v>
       </c>
       <c r="I7">
-        <v>20.63</v>
+        <v>21.1</v>
       </c>
       <c r="J7">
-        <v>0.05</v>
+        <v>-0.18</v>
       </c>
       <c r="K7" t="str">
-        <v>(0.24%)</v>
+        <v>(-0.85%)</v>
       </c>
       <c r="L7">
-        <v>17.6873270772127</v>
+        <v>20.36852163495823</v>
       </c>
       <c r="M7">
         <v>3.624820361867181</v>
@@ -757,16 +757,16 @@
         <v>371.33569240624996</v>
       </c>
       <c r="I8">
-        <v>464.62</v>
+        <v>472.99</v>
       </c>
       <c r="J8">
-        <v>-10.21</v>
+        <v>-2.9</v>
       </c>
       <c r="K8" t="str">
-        <v>(-2.15%)</v>
+        <v>(-0.61%)</v>
       </c>
       <c r="L8">
-        <v>25.121287692348954</v>
+        <v>27.375312869881046</v>
       </c>
       <c r="M8">
         <v>1.2285805563624501</v>
@@ -804,16 +804,16 @@
         <v>122.74421769642858</v>
       </c>
       <c r="I9">
-        <v>143.21</v>
+        <v>151.49</v>
       </c>
       <c r="J9">
-        <v>-0.81</v>
+        <v>0.24</v>
       </c>
       <c r="K9" t="str">
-        <v>(-0.56%)</v>
+        <v>(0.16%)</v>
       </c>
       <c r="L9">
-        <v>16.67352050276411</v>
+        <v>23.4192557849573</v>
       </c>
       <c r="M9">
         <v>3.5534158729596457</v>
@@ -851,16 +851,16 @@
         <v>836.69580625</v>
       </c>
       <c r="I10">
-        <v>926.95</v>
+        <v>900</v>
       </c>
       <c r="J10">
-        <v>5.29</v>
+        <v>-2.13</v>
       </c>
       <c r="K10" t="str">
-        <v>(0.57%)</v>
+        <v>(-0.24%)</v>
       </c>
       <c r="L10">
-        <v>10.786978143766692</v>
+        <v>7.5659747876261045</v>
       </c>
       <c r="M10">
         <v>1.3841225340980075</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -898,13 +898,13 @@
         <v>1470.8712083333332</v>
       </c>
       <c r="I11" t="str">
-        <v>1,715.57</v>
+        <v>1,889.94</v>
       </c>
       <c r="J11">
-        <v>12.57</v>
+        <v>81.51</v>
       </c>
       <c r="K11" t="str">
-        <v>(0.74%)</v>
+        <v>(4.51%)</v>
       </c>
       <c r="M11">
         <v>1.8249159094044385</v>
@@ -942,16 +942,16 @@
         <v>260.4535</v>
       </c>
       <c r="I12">
-        <v>277.88</v>
+        <v>278.5</v>
       </c>
       <c r="J12">
-        <v>-4.98</v>
+        <v>1.27</v>
       </c>
       <c r="K12" t="str">
-        <v>(-1.76%)</v>
+        <v>(0.46%)</v>
       </c>
       <c r="L12">
-        <v>6.690829649054428</v>
+        <v>6.928875979781411</v>
       </c>
       <c r="M12">
         <v>0.10771524003760219</v>
@@ -989,16 +989,16 @@
         <v>54.09815</v>
       </c>
       <c r="I13">
-        <v>54.37</v>
+        <v>56.35</v>
       </c>
       <c r="J13">
-        <v>-0.03</v>
+        <v>-0.33</v>
       </c>
       <c r="K13" t="str">
-        <v>(-0.05%)</v>
+        <v>(-0.58%)</v>
       </c>
       <c r="L13">
-        <v>0.5025125628140715</v>
+        <v>4.162526814687757</v>
       </c>
       <c r="M13">
         <v>0.022373265142684617</v>

--- a/electron/data/summary.xlsx
+++ b/electron/data/summary.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -451,60 +451,60 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>EFERT</v>
+        <v>MARI</v>
       </c>
       <c r="B2" t="str">
         <v>Equity</v>
       </c>
       <c r="C2" t="str">
-        <v>Engro Fertilizers Limited</v>
+        <v>Mari Energies Limited</v>
       </c>
       <c r="D2" t="str">
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>FERTILIZER</v>
+        <v>OIL &amp; GAS EXPLORATION COMPANIES</v>
       </c>
       <c r="F2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>25213.5823185</v>
+        <v>50086.75</v>
       </c>
       <c r="H2">
-        <v>178.81973275531917</v>
+        <v>500.8675</v>
       </c>
       <c r="I2">
-        <v>219.49</v>
+        <v>762.1</v>
       </c>
       <c r="J2">
-        <v>-2.19</v>
+        <v>-8.77</v>
       </c>
       <c r="K2" t="str">
-        <v>(-0.99%)</v>
+        <v>(-1.14%)</v>
       </c>
       <c r="L2">
-        <v>22.74372443019495</v>
+        <v>52.15600932382317</v>
       </c>
       <c r="M2">
-        <v>10.42753148506382</v>
+        <v>83.33277874368807</v>
       </c>
       <c r="N2">
         <v>0</v>
       </c>
       <c r="O2">
-        <v>678.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MEBL</v>
+        <v>HBL</v>
       </c>
       <c r="B3" t="str">
         <v>Equity</v>
       </c>
       <c r="C3" t="str">
-        <v>Meezan Bank Limited</v>
+        <v>Habib Bank Limited</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -513,506 +513,39 @@
         <v>COMMERCIAL BANKS</v>
       </c>
       <c r="F3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>89086.05425822221</v>
+        <v>10017.75</v>
       </c>
       <c r="H3">
-        <v>222.71513564555553</v>
+        <v>100.1775</v>
       </c>
       <c r="I3">
-        <v>437</v>
+        <v>306.95</v>
       </c>
       <c r="J3">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="str">
-        <v>(0.23%)</v>
+        <v>(0.95%)</v>
       </c>
       <c r="L3">
-        <v>96.21477396824632</v>
+        <v>206.40612912081053</v>
       </c>
       <c r="M3">
-        <v>36.84314366452076</v>
+        <v>16.667221256311922</v>
       </c>
       <c r="N3">
-        <v>8611.5</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>6650</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>MIIETF</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Mahaana Islamic Index ETF</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v>EXCHANGE TRADED FUNDS</v>
-      </c>
-      <c r="F4">
-        <v>1500</v>
-      </c>
-      <c r="G4">
-        <v>21174.25</v>
-      </c>
-      <c r="H4">
-        <v>14.116166666666667</v>
-      </c>
-      <c r="I4">
-        <v>17.45</v>
-      </c>
-      <c r="J4">
-        <v>-0.11</v>
-      </c>
-      <c r="K4" t="str">
-        <v>(-0.63%)</v>
-      </c>
-      <c r="L4">
-        <v>23.617129296197028</v>
-      </c>
-      <c r="M4">
-        <v>8.756992788986127</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>MARI</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Mari Energies Limited</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v>OIL &amp; GAS EXPLORATION COMPANIES</v>
-      </c>
-      <c r="F5">
-        <v>99</v>
-      </c>
-      <c r="G5">
-        <v>59585.702485</v>
-      </c>
-      <c r="H5">
-        <v>601.8757826767677</v>
-      </c>
-      <c r="I5">
-        <v>760.9</v>
-      </c>
-      <c r="J5">
-        <v>19.86</v>
-      </c>
-      <c r="K5" t="str">
-        <v>(2.68%)</v>
-      </c>
-      <c r="L5">
-        <v>26.42143477114029</v>
-      </c>
-      <c r="M5">
-        <v>24.64274139522381</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>DCR</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Dolmen City REIT</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v>REAL ESTATE INVESTMENT TRUST</v>
-      </c>
-      <c r="F6">
-        <v>710</v>
-      </c>
-      <c r="G6">
-        <v>18337.12095</v>
-      </c>
-      <c r="H6">
-        <v>25.82693091549296</v>
-      </c>
-      <c r="I6">
-        <v>32</v>
-      </c>
-      <c r="J6">
-        <v>-0.09</v>
-      </c>
-      <c r="K6" t="str">
-        <v>(-0.28%)</v>
-      </c>
-      <c r="L6">
-        <v>23.90167497913569</v>
-      </c>
-      <c r="M6">
-        <v>7.583646926333468</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>409.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>MZNPETF</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Meezan Pakistan ETF</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v>EXCHANGE TRADED FUNDS</v>
-      </c>
-      <c r="F7">
-        <v>500</v>
-      </c>
-      <c r="G7">
-        <v>8764.75</v>
-      </c>
-      <c r="H7">
-        <v>17.5295</v>
-      </c>
-      <c r="I7">
-        <v>21.1</v>
-      </c>
-      <c r="J7">
-        <v>-0.18</v>
-      </c>
-      <c r="K7" t="str">
-        <v>(-0.85%)</v>
-      </c>
-      <c r="L7">
-        <v>20.36852163495823</v>
-      </c>
-      <c r="M7">
-        <v>3.624820361867181</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>LUCK</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Lucky Cement Limited</v>
-      </c>
-      <c r="D8" t="str">
-        <v>XD</v>
-      </c>
-      <c r="E8" t="str">
-        <v>CEMENT</v>
-      </c>
-      <c r="F8">
-        <v>8</v>
-      </c>
-      <c r="G8">
-        <v>2970.6855392499997</v>
-      </c>
-      <c r="H8">
-        <v>371.33569240624996</v>
-      </c>
-      <c r="I8">
-        <v>472.99</v>
-      </c>
-      <c r="J8">
-        <v>-2.9</v>
-      </c>
-      <c r="K8" t="str">
-        <v>(-0.61%)</v>
-      </c>
-      <c r="L8">
-        <v>27.375312869881046</v>
-      </c>
-      <c r="M8">
-        <v>1.2285805563624501</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>SYS</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Systems Limited</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v>TECHNOLOGY &amp; COMMUNICATION</v>
-      </c>
-      <c r="F9">
-        <v>70</v>
-      </c>
-      <c r="G9">
-        <v>8592.09523875</v>
-      </c>
-      <c r="H9">
-        <v>122.74421769642858</v>
-      </c>
-      <c r="I9">
-        <v>151.49</v>
-      </c>
-      <c r="J9">
-        <v>0.24</v>
-      </c>
-      <c r="K9" t="str">
-        <v>(0.16%)</v>
-      </c>
-      <c r="L9">
-        <v>23.4192557849573</v>
-      </c>
-      <c r="M9">
-        <v>3.5534158729596457</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>HALEON</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Haleon Pakistan Limited</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v>PHARMACEUTICALS</v>
-      </c>
-      <c r="F10">
-        <v>4</v>
-      </c>
-      <c r="G10">
-        <v>3346.783225</v>
-      </c>
-      <c r="H10">
-        <v>836.69580625</v>
-      </c>
-      <c r="I10">
-        <v>900</v>
-      </c>
-      <c r="J10">
-        <v>-2.13</v>
-      </c>
-      <c r="K10" t="str">
-        <v>(-0.24%)</v>
-      </c>
-      <c r="L10">
-        <v>7.5659747876261045</v>
-      </c>
-      <c r="M10">
-        <v>1.3841225340980075</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>SAZEW</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Sazgar Engineering Works Limited</v>
-      </c>
-      <c r="D11" t="str">
-        <v>XD</v>
-      </c>
-      <c r="E11" t="str">
-        <v>AUTOMOBILE ASSEMBLER</v>
-      </c>
-      <c r="F11">
-        <v>3</v>
-      </c>
-      <c r="G11">
-        <v>4412.613625</v>
-      </c>
-      <c r="H11">
-        <v>1470.8712083333332</v>
-      </c>
-      <c r="I11" t="str">
-        <v>1,889.94</v>
-      </c>
-      <c r="J11">
-        <v>81.51</v>
-      </c>
-      <c r="K11" t="str">
-        <v>(4.51%)</v>
-      </c>
-      <c r="M11">
-        <v>1.8249159094044385</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>OGDC</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Oil &amp; Gas Development Company Limited</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v>OIL &amp; GAS EXPLORATION COMPANIES</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>260.4535</v>
-      </c>
-      <c r="H12">
-        <v>260.4535</v>
-      </c>
-      <c r="I12">
-        <v>278.5</v>
-      </c>
-      <c r="J12">
-        <v>1.27</v>
-      </c>
-      <c r="K12" t="str">
-        <v>(0.46%)</v>
-      </c>
-      <c r="L12">
-        <v>6.928875979781411</v>
-      </c>
-      <c r="M12">
-        <v>0.10771524003760219</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>PAEL</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Equity</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Pak Elektron Limited</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v>CABLE &amp; ELECTRICAL GOODS</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>54.09815</v>
-      </c>
-      <c r="H13">
-        <v>54.09815</v>
-      </c>
-      <c r="I13">
-        <v>56.35</v>
-      </c>
-      <c r="J13">
-        <v>-0.33</v>
-      </c>
-      <c r="K13" t="str">
-        <v>(-0.58%)</v>
-      </c>
-      <c r="L13">
-        <v>4.162526814687757</v>
-      </c>
-      <c r="M13">
-        <v>0.022373265142684617</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P3"/>
   </ignoredErrors>
 </worksheet>
 </file>